--- a/finance/_refresh_bolt.xlsx
+++ b/finance/_refresh_bolt.xlsx
@@ -1313,7 +1313,7 @@
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>Cap on revenue sailings/day — ~1 sailing/70min in a 12h window; a believable on-demand premium duty cycle, not capacity-max (Jaideep 2026-06-19).</t>
+          <t>Cap on revenue sailings/day — MID headline duty cycle; thin=12 / full=18 bookends in _utilization_scenarios (Jaideep 2026-06-21).</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
         <v>0.45</v>
       </c>
       <c r="C31" s="19" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="F31" s="14" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>0.55</v>
       </c>
       <c r="C32" s="19" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>0.7</v>
       </c>
       <c r="C33" s="19" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v/>
       </c>
       <c r="K4" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J4,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J4,1))</f>
         <v/>
       </c>
       <c r="L4" s="34">
@@ -2882,7 +2882,7 @@
         <v/>
       </c>
       <c r="K5" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J5,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J5,1))</f>
         <v/>
       </c>
       <c r="L5" s="34">
@@ -3062,7 +3062,7 @@
         <v/>
       </c>
       <c r="K6" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J6,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J6,1))</f>
         <v/>
       </c>
       <c r="L6" s="34">
@@ -3242,7 +3242,7 @@
         <v/>
       </c>
       <c r="K7" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J7,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J7,1))</f>
         <v/>
       </c>
       <c r="L7" s="34">
@@ -3414,7 +3414,7 @@
         <v/>
       </c>
       <c r="K8" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J8,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J8,1))</f>
         <v/>
       </c>
       <c r="L8" s="34">
@@ -3590,7 +3590,7 @@
         <v/>
       </c>
       <c r="K9" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J9,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J9,1))</f>
         <v/>
       </c>
       <c r="L9" s="34">
@@ -3772,7 +3772,7 @@
         <v/>
       </c>
       <c r="K10" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J10,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J10,1))</f>
         <v/>
       </c>
       <c r="L10" s="34">
@@ -3952,7 +3952,7 @@
         <v/>
       </c>
       <c r="K11" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J11,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J11,1))</f>
         <v/>
       </c>
       <c r="L11" s="34">
@@ -4134,7 +4134,7 @@
         <v/>
       </c>
       <c r="K12" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J12,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J12,1))</f>
         <v/>
       </c>
       <c r="L12" s="34">
@@ -4316,7 +4316,7 @@
         <v/>
       </c>
       <c r="K13" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J13,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J13,1))</f>
         <v/>
       </c>
       <c r="L13" s="34">
@@ -4498,7 +4498,7 @@
         <v/>
       </c>
       <c r="K14" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J14,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J14,1))</f>
         <v/>
       </c>
       <c r="L14" s="34">
@@ -4678,7 +4678,7 @@
         <v/>
       </c>
       <c r="K15" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J15,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J15,1))</f>
         <v/>
       </c>
       <c r="L15" s="34">
@@ -4860,7 +4860,7 @@
         <v/>
       </c>
       <c r="K16" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J16,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J16,1))</f>
         <v/>
       </c>
       <c r="L16" s="34">
@@ -5032,7 +5032,7 @@
         <v/>
       </c>
       <c r="K17" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J17,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J17,1))</f>
         <v/>
       </c>
       <c r="L17" s="34">
@@ -5208,7 +5208,7 @@
         <v/>
       </c>
       <c r="K18" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J18,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J18,1))</f>
         <v/>
       </c>
       <c r="L18" s="34">
@@ -5388,7 +5388,7 @@
         <v/>
       </c>
       <c r="K19" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J19,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J19,1))</f>
         <v/>
       </c>
       <c r="L19" s="34">
@@ -5568,7 +5568,7 @@
         <v/>
       </c>
       <c r="K20" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J20,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J20,1))</f>
         <v/>
       </c>
       <c r="L20" s="34">
@@ -5750,7 +5750,7 @@
         <v/>
       </c>
       <c r="K21" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J21,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J21,1))</f>
         <v/>
       </c>
       <c r="L21" s="34">
@@ -5930,7 +5930,7 @@
         <v/>
       </c>
       <c r="K22" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J22,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J22,1))</f>
         <v/>
       </c>
       <c r="L22" s="34">
@@ -6112,7 +6112,7 @@
         <v/>
       </c>
       <c r="K23" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J23,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J23,1))</f>
         <v/>
       </c>
       <c r="L23" s="34">
@@ -6292,7 +6292,7 @@
         <v/>
       </c>
       <c r="K24" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J24,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J24,1))</f>
         <v/>
       </c>
       <c r="L24" s="34">
@@ -6478,7 +6478,7 @@
         <v/>
       </c>
       <c r="K25" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J25,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J25,1))</f>
         <v/>
       </c>
       <c r="L25" s="34">
@@ -6658,7 +6658,7 @@
         <v/>
       </c>
       <c r="K26" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J26,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J26,1))</f>
         <v/>
       </c>
       <c r="L26" s="34">
@@ -6838,7 +6838,7 @@
         <v/>
       </c>
       <c r="K27" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J27,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J27,1))</f>
         <v/>
       </c>
       <c r="L27" s="34">
@@ -7018,7 +7018,7 @@
         <v/>
       </c>
       <c r="K28" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J28,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J28,1))</f>
         <v/>
       </c>
       <c r="L28" s="34">
@@ -7198,7 +7198,7 @@
         <v/>
       </c>
       <c r="K29" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J29,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J29,1))</f>
         <v/>
       </c>
       <c r="L29" s="34">
@@ -7378,7 +7378,7 @@
         <v/>
       </c>
       <c r="K30" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J30,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J30,1))</f>
         <v/>
       </c>
       <c r="L30" s="34">
@@ -7560,7 +7560,7 @@
         <v/>
       </c>
       <c r="K31" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J31,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J31,1))</f>
         <v/>
       </c>
       <c r="L31" s="34">
@@ -7740,7 +7740,7 @@
         <v/>
       </c>
       <c r="K32" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J32,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J32,1))</f>
         <v/>
       </c>
       <c r="L32" s="34">
@@ -7920,7 +7920,7 @@
         <v/>
       </c>
       <c r="K33" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J33,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J33,1))</f>
         <v/>
       </c>
       <c r="L33" s="34">
@@ -8106,7 +8106,7 @@
         <v/>
       </c>
       <c r="K34" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J34,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J34,1))</f>
         <v/>
       </c>
       <c r="L34" s="34">
@@ -8288,7 +8288,7 @@
         <v/>
       </c>
       <c r="K35" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J35,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J35,1))</f>
         <v/>
       </c>
       <c r="L35" s="34">
@@ -8470,7 +8470,7 @@
         <v/>
       </c>
       <c r="K36" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J36,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J36,1))</f>
         <v/>
       </c>
       <c r="L36" s="34">
@@ -8650,7 +8650,7 @@
         <v/>
       </c>
       <c r="K37" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J37,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J37,1))</f>
         <v/>
       </c>
       <c r="L37" s="34">
@@ -8844,7 +8844,7 @@
         <v/>
       </c>
       <c r="K38" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J38,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J38,1))</f>
         <v/>
       </c>
       <c r="L38" s="34">
@@ -9036,7 +9036,7 @@
         <v/>
       </c>
       <c r="K39" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J39,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J39,1))</f>
         <v/>
       </c>
       <c r="L39" s="34">
@@ -9212,7 +9212,7 @@
         <v/>
       </c>
       <c r="K40" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J40,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J40,1))</f>
         <v/>
       </c>
       <c r="L40" s="34">
@@ -9378,7 +9378,7 @@
         <v/>
       </c>
       <c r="K41" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J41,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J41,1))</f>
         <v/>
       </c>
       <c r="L41" s="34">
@@ -9554,7 +9554,7 @@
         <v/>
       </c>
       <c r="K42" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J42,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J42,1))</f>
         <v/>
       </c>
       <c r="L42" s="34">
@@ -9740,7 +9740,7 @@
         <v/>
       </c>
       <c r="K43" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J43,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J43,1))</f>
         <v/>
       </c>
       <c r="L43" s="34">
@@ -9922,7 +9922,7 @@
         <v/>
       </c>
       <c r="K44" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J44,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J44,1))</f>
         <v/>
       </c>
       <c r="L44" s="34">
@@ -10108,7 +10108,7 @@
         <v/>
       </c>
       <c r="K45" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J45,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J45,1))</f>
         <v/>
       </c>
       <c r="L45" s="34">
@@ -10288,7 +10288,7 @@
         <v/>
       </c>
       <c r="K46" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J46,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J46,1))</f>
         <v/>
       </c>
       <c r="L46" s="34">
@@ -10470,7 +10470,7 @@
         <v/>
       </c>
       <c r="K47" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J47,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J47,1))</f>
         <v/>
       </c>
       <c r="L47" s="34">
@@ -10650,7 +10650,7 @@
         <v/>
       </c>
       <c r="K48" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J48,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J48,1))</f>
         <v/>
       </c>
       <c r="L48" s="34">
@@ -10832,7 +10832,7 @@
         <v/>
       </c>
       <c r="K49" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J49,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J49,1))</f>
         <v/>
       </c>
       <c r="L49" s="34">
@@ -11012,7 +11012,7 @@
         <v/>
       </c>
       <c r="K50" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J50,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J50,1))</f>
         <v/>
       </c>
       <c r="L50" s="34">
@@ -11184,7 +11184,7 @@
         <v/>
       </c>
       <c r="K51" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J51,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J51,1))</f>
         <v/>
       </c>
       <c r="L51" s="34">
@@ -11360,7 +11360,7 @@
         <v/>
       </c>
       <c r="K52" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J52,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J52,1))</f>
         <v/>
       </c>
       <c r="L52" s="34">
@@ -11546,7 +11546,7 @@
         <v/>
       </c>
       <c r="K53" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J53,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J53,1))</f>
         <v/>
       </c>
       <c r="L53" s="34">
@@ -11718,7 +11718,7 @@
         <v/>
       </c>
       <c r="K54" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J54,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J54,1))</f>
         <v/>
       </c>
       <c r="L54" s="34">
@@ -11886,7 +11886,7 @@
         <v/>
       </c>
       <c r="K55" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J55,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J55,1))</f>
         <v/>
       </c>
       <c r="L55" s="34">
@@ -12052,7 +12052,7 @@
         <v/>
       </c>
       <c r="K56" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J56,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J56,1))</f>
         <v/>
       </c>
       <c r="L56" s="34">
@@ -12230,7 +12230,7 @@
         <v/>
       </c>
       <c r="K57" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J57,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J57,1))</f>
         <v/>
       </c>
       <c r="L57" s="34">
@@ -12412,7 +12412,7 @@
         <v/>
       </c>
       <c r="K58" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J58,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J58,1))</f>
         <v/>
       </c>
       <c r="L58" s="34">
@@ -12588,7 +12588,7 @@
         <v/>
       </c>
       <c r="K59" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J59,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J59,1))</f>
         <v/>
       </c>
       <c r="L59" s="34">
@@ -12764,7 +12764,7 @@
         <v/>
       </c>
       <c r="K60" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J60,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J60,1))</f>
         <v/>
       </c>
       <c r="L60" s="34">
@@ -12936,7 +12936,7 @@
         <v/>
       </c>
       <c r="K61" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J61,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J61,1))</f>
         <v/>
       </c>
       <c r="L61" s="34">
@@ -13114,7 +13114,7 @@
         <v/>
       </c>
       <c r="K62" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J62,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J62,1))</f>
         <v/>
       </c>
       <c r="L62" s="34">
@@ -13296,7 +13296,7 @@
         <v/>
       </c>
       <c r="K63" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J63,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J63,1))</f>
         <v/>
       </c>
       <c r="L63" s="34">
@@ -13478,7 +13478,7 @@
         <v/>
       </c>
       <c r="K64" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J64,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J64,1))</f>
         <v/>
       </c>
       <c r="L64" s="34">
@@ -13650,7 +13650,7 @@
         <v/>
       </c>
       <c r="K65" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J65,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J65,1))</f>
         <v/>
       </c>
       <c r="L65" s="34">
@@ -13826,7 +13826,7 @@
         <v/>
       </c>
       <c r="K66" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J66,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J66,1))</f>
         <v/>
       </c>
       <c r="L66" s="34">
@@ -13996,7 +13996,7 @@
         <v/>
       </c>
       <c r="K67" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J67,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J67,1))</f>
         <v/>
       </c>
       <c r="L67" s="34">
@@ -14174,7 +14174,7 @@
         <v/>
       </c>
       <c r="K68" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J68,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J68,1))</f>
         <v/>
       </c>
       <c r="L68" s="34">
@@ -14356,7 +14356,7 @@
         <v/>
       </c>
       <c r="K69" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J69,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J69,1))</f>
         <v/>
       </c>
       <c r="L69" s="34">
@@ -14536,7 +14536,7 @@
         <v/>
       </c>
       <c r="K70" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J70,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J70,1))</f>
         <v/>
       </c>
       <c r="L70" s="34">
@@ -14716,7 +14716,7 @@
         <v/>
       </c>
       <c r="K71" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J71,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J71,1))</f>
         <v/>
       </c>
       <c r="L71" s="34">
@@ -14886,7 +14886,7 @@
         <v/>
       </c>
       <c r="K72" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J72,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J72,1))</f>
         <v/>
       </c>
       <c r="L72" s="34">
@@ -15062,7 +15062,7 @@
         <v/>
       </c>
       <c r="K73" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J73,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J73,1))</f>
         <v/>
       </c>
       <c r="L73" s="34">
@@ -15242,7 +15242,7 @@
         <v/>
       </c>
       <c r="K74" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J74,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J74,1))</f>
         <v/>
       </c>
       <c r="L74" s="34">
@@ -15422,7 +15422,7 @@
         <v/>
       </c>
       <c r="K75" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J75,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J75,1))</f>
         <v/>
       </c>
       <c r="L75" s="34">
@@ -15610,7 +15610,7 @@
         <v/>
       </c>
       <c r="K76" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J76,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J76,1))</f>
         <v/>
       </c>
       <c r="L76" s="34">
@@ -15790,7 +15790,7 @@
         <v/>
       </c>
       <c r="K77" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J77,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J77,1))</f>
         <v/>
       </c>
       <c r="L77" s="34">
@@ -15970,7 +15970,7 @@
         <v/>
       </c>
       <c r="K78" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J78,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J78,1))</f>
         <v/>
       </c>
       <c r="L78" s="34">
@@ -16150,7 +16150,7 @@
         <v/>
       </c>
       <c r="K79" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J79,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J79,1))</f>
         <v/>
       </c>
       <c r="L79" s="34">
@@ -16330,7 +16330,7 @@
         <v/>
       </c>
       <c r="K80" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J80,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J80,1))</f>
         <v/>
       </c>
       <c r="L80" s="34">
@@ -16512,7 +16512,7 @@
         <v/>
       </c>
       <c r="K81" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J81,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J81,1))</f>
         <v/>
       </c>
       <c r="L81" s="34">
@@ -16694,7 +16694,7 @@
         <v/>
       </c>
       <c r="K82" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J82,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J82,1))</f>
         <v/>
       </c>
       <c r="L82" s="34">
@@ -16874,7 +16874,7 @@
         <v/>
       </c>
       <c r="K83" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J83,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J83,1))</f>
         <v/>
       </c>
       <c r="L83" s="34">
@@ -17054,7 +17054,7 @@
         <v/>
       </c>
       <c r="K84" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J84,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J84,1))</f>
         <v/>
       </c>
       <c r="L84" s="34">
@@ -17234,7 +17234,7 @@
         <v/>
       </c>
       <c r="K85" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J85,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J85,1))</f>
         <v/>
       </c>
       <c r="L85" s="34">
@@ -17414,7 +17414,7 @@
         <v/>
       </c>
       <c r="K86" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J86,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J86,1))</f>
         <v/>
       </c>
       <c r="L86" s="34">
@@ -17596,7 +17596,7 @@
         <v/>
       </c>
       <c r="K87" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J87,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J87,1))</f>
         <v/>
       </c>
       <c r="L87" s="34">
@@ -17778,7 +17778,7 @@
         <v/>
       </c>
       <c r="K88" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J88,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J88,1))</f>
         <v/>
       </c>
       <c r="L88" s="34">
@@ -17948,7 +17948,7 @@
         <v/>
       </c>
       <c r="K89" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J89,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J89,1))</f>
         <v/>
       </c>
       <c r="L89" s="34">
@@ -18126,7 +18126,7 @@
         <v/>
       </c>
       <c r="K90" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J90,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J90,1))</f>
         <v/>
       </c>
       <c r="L90" s="34">
@@ -18308,7 +18308,7 @@
         <v/>
       </c>
       <c r="K91" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J91,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J91,1))</f>
         <v/>
       </c>
       <c r="L91" s="34">
@@ -18490,7 +18490,7 @@
         <v/>
       </c>
       <c r="K92" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J92,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J92,1))</f>
         <v/>
       </c>
       <c r="L92" s="34">
@@ -18672,7 +18672,7 @@
         <v/>
       </c>
       <c r="K93" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J93,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J93,1))</f>
         <v/>
       </c>
       <c r="L93" s="34">
@@ -18852,7 +18852,7 @@
         <v/>
       </c>
       <c r="K94" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J94,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J94,1))</f>
         <v/>
       </c>
       <c r="L94" s="34">
@@ -19034,7 +19034,7 @@
         <v/>
       </c>
       <c r="K95" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J95,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J95,1))</f>
         <v/>
       </c>
       <c r="L95" s="34">
@@ -19216,7 +19216,7 @@
         <v/>
       </c>
       <c r="K96" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J96,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J96,1))</f>
         <v/>
       </c>
       <c r="L96" s="34">
@@ -19398,7 +19398,7 @@
         <v/>
       </c>
       <c r="K97" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J97,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J97,1))</f>
         <v/>
       </c>
       <c r="L97" s="34">
@@ -19580,7 +19580,7 @@
         <v/>
       </c>
       <c r="K98" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J98,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J98,1))</f>
         <v/>
       </c>
       <c r="L98" s="34">
@@ -19760,7 +19760,7 @@
         <v/>
       </c>
       <c r="K99" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J99,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J99,1))</f>
         <v/>
       </c>
       <c r="L99" s="34">
@@ -19942,7 +19942,7 @@
         <v/>
       </c>
       <c r="K100" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J100,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J100,1))</f>
         <v/>
       </c>
       <c r="L100" s="34">
@@ -20124,7 +20124,7 @@
         <v/>
       </c>
       <c r="K101" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J101,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J101,1))</f>
         <v/>
       </c>
       <c r="L101" s="34">
@@ -20306,7 +20306,7 @@
         <v/>
       </c>
       <c r="K102" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J102,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J102,1))</f>
         <v/>
       </c>
       <c r="L102" s="34">
@@ -20478,7 +20478,7 @@
         <v/>
       </c>
       <c r="K103" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J103,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J103,1))</f>
         <v/>
       </c>
       <c r="L103" s="34">
@@ -20656,7 +20656,7 @@
         <v/>
       </c>
       <c r="K104" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J104,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J104,1))</f>
         <v/>
       </c>
       <c r="L104" s="34">
@@ -20838,7 +20838,7 @@
         <v/>
       </c>
       <c r="K105" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J105,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J105,1))</f>
         <v/>
       </c>
       <c r="L105" s="34">
@@ -21020,7 +21020,7 @@
         <v/>
       </c>
       <c r="K106" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J106,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J106,1))</f>
         <v/>
       </c>
       <c r="L106" s="34">
@@ -21202,7 +21202,7 @@
         <v/>
       </c>
       <c r="K107" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J107,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J107,1))</f>
         <v/>
       </c>
       <c r="L107" s="34">
@@ -21382,7 +21382,7 @@
         <v/>
       </c>
       <c r="K108" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J108,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J108,1))</f>
         <v/>
       </c>
       <c r="L108" s="34">
@@ -21564,7 +21564,7 @@
         <v/>
       </c>
       <c r="K109" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J109,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J109,1))</f>
         <v/>
       </c>
       <c r="L109" s="34">
@@ -21744,7 +21744,7 @@
         <v/>
       </c>
       <c r="K110" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J110,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J110,1))</f>
         <v/>
       </c>
       <c r="L110" s="34">
@@ -21916,7 +21916,7 @@
         <v/>
       </c>
       <c r="K111" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J111,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J111,1))</f>
         <v/>
       </c>
       <c r="L111" s="34">
@@ -22092,7 +22092,7 @@
         <v/>
       </c>
       <c r="K112" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J112,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J112,1))</f>
         <v/>
       </c>
       <c r="L112" s="34">
@@ -22274,7 +22274,7 @@
         <v/>
       </c>
       <c r="K113" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J113,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J113,1))</f>
         <v/>
       </c>
       <c r="L113" s="34">
@@ -22454,7 +22454,7 @@
         <v/>
       </c>
       <c r="K114" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J114,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J114,1))</f>
         <v/>
       </c>
       <c r="L114" s="34">
@@ -22634,7 +22634,7 @@
         <v/>
       </c>
       <c r="K115" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J115,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J115,1))</f>
         <v/>
       </c>
       <c r="L115" s="34">
@@ -22820,7 +22820,7 @@
         <v/>
       </c>
       <c r="K116" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J116,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J116,1))</f>
         <v/>
       </c>
       <c r="L116" s="34">
@@ -23006,7 +23006,7 @@
         <v/>
       </c>
       <c r="K117" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J117,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J117,1))</f>
         <v/>
       </c>
       <c r="L117" s="34">
@@ -23186,7 +23186,7 @@
         <v/>
       </c>
       <c r="K118" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J118,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J118,1))</f>
         <v/>
       </c>
       <c r="L118" s="34">
@@ -23366,7 +23366,7 @@
         <v/>
       </c>
       <c r="K119" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J119,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J119,1))</f>
         <v/>
       </c>
       <c r="L119" s="34">
@@ -23552,7 +23552,7 @@
         <v/>
       </c>
       <c r="K120" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J120,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J120,1))</f>
         <v/>
       </c>
       <c r="L120" s="34">
@@ -23738,7 +23738,7 @@
         <v/>
       </c>
       <c r="K121" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J121,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J121,1))</f>
         <v/>
       </c>
       <c r="L121" s="34">
@@ -23918,7 +23918,7 @@
         <v/>
       </c>
       <c r="K122" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J122,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J122,1))</f>
         <v/>
       </c>
       <c r="L122" s="34">
@@ -24094,7 +24094,7 @@
         <v/>
       </c>
       <c r="K123" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J123,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J123,1))</f>
         <v/>
       </c>
       <c r="L123" s="34">
@@ -24262,7 +24262,7 @@
         <v/>
       </c>
       <c r="K124" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J124,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J124,1))</f>
         <v/>
       </c>
       <c r="L124" s="34">
@@ -24428,7 +24428,7 @@
         <v/>
       </c>
       <c r="K125" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J125,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J125,1))</f>
         <v/>
       </c>
       <c r="L125" s="34">
@@ -24604,7 +24604,7 @@
         <v/>
       </c>
       <c r="K126" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J126,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J126,1))</f>
         <v/>
       </c>
       <c r="L126" s="34">
@@ -24788,7 +24788,7 @@
         <v/>
       </c>
       <c r="K127" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J127,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J127,1))</f>
         <v/>
       </c>
       <c r="L127" s="34">
@@ -24964,7 +24964,7 @@
         <v/>
       </c>
       <c r="K128" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J128,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J128,1))</f>
         <v/>
       </c>
       <c r="L128" s="34">
@@ -25158,7 +25158,7 @@
         <v/>
       </c>
       <c r="K129" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J129,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J129,1))</f>
         <v/>
       </c>
       <c r="L129" s="34">
@@ -25342,7 +25342,7 @@
         <v/>
       </c>
       <c r="K130" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J130,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J130,1))</f>
         <v/>
       </c>
       <c r="L130" s="34">
@@ -25508,7 +25508,7 @@
         <v/>
       </c>
       <c r="K131" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J131,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J131,1))</f>
         <v/>
       </c>
       <c r="L131" s="34">
@@ -25674,7 +25674,7 @@
         <v/>
       </c>
       <c r="K132" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J132,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J132,1))</f>
         <v/>
       </c>
       <c r="L132" s="34">
@@ -25850,7 +25850,7 @@
         <v/>
       </c>
       <c r="K133" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J133,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J133,1))</f>
         <v/>
       </c>
       <c r="L133" s="34">
@@ -26032,7 +26032,7 @@
         <v/>
       </c>
       <c r="K134" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J134,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J134,1))</f>
         <v/>
       </c>
       <c r="L134" s="34">
@@ -26214,7 +26214,7 @@
         <v/>
       </c>
       <c r="K135" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J135,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J135,1))</f>
         <v/>
       </c>
       <c r="L135" s="34">
@@ -26394,7 +26394,7 @@
         <v/>
       </c>
       <c r="K136" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J136,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J136,1))</f>
         <v/>
       </c>
       <c r="L136" s="34">
@@ -26566,7 +26566,7 @@
         <v/>
       </c>
       <c r="K137" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J137,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J137,1))</f>
         <v/>
       </c>
       <c r="L137" s="34">
@@ -26732,7 +26732,7 @@
         <v/>
       </c>
       <c r="K138" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J138,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J138,1))</f>
         <v/>
       </c>
       <c r="L138" s="34">
@@ -26908,7 +26908,7 @@
         <v/>
       </c>
       <c r="K139" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J139,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J139,1))</f>
         <v/>
       </c>
       <c r="L139" s="34">
@@ -27090,7 +27090,7 @@
         <v/>
       </c>
       <c r="K140" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J140,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J140,1))</f>
         <v/>
       </c>
       <c r="L140" s="34">
@@ -27270,7 +27270,7 @@
         <v/>
       </c>
       <c r="K141" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J141,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J141,1))</f>
         <v/>
       </c>
       <c r="L141" s="34">
@@ -27440,7 +27440,7 @@
         <v/>
       </c>
       <c r="K142" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J142,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J142,1))</f>
         <v/>
       </c>
       <c r="L142" s="34">
@@ -27616,7 +27616,7 @@
         <v/>
       </c>
       <c r="K143" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J143,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J143,1))</f>
         <v/>
       </c>
       <c r="L143" s="34">
@@ -27798,7 +27798,7 @@
         <v/>
       </c>
       <c r="K144" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J144,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J144,1))</f>
         <v/>
       </c>
       <c r="L144" s="34">
@@ -27990,7 +27990,7 @@
         <v/>
       </c>
       <c r="K145" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J145,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J145,1))</f>
         <v/>
       </c>
       <c r="L145" s="34">
@@ -28184,7 +28184,7 @@
         <v/>
       </c>
       <c r="K146" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J146,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J146,1))</f>
         <v/>
       </c>
       <c r="L146" s="34">
@@ -28368,7 +28368,7 @@
         <v/>
       </c>
       <c r="K147" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J147,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J147,1))</f>
         <v/>
       </c>
       <c r="L147" s="34">
@@ -28544,7 +28544,7 @@
         <v/>
       </c>
       <c r="K148" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J148,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J148,1))</f>
         <v/>
       </c>
       <c r="L148" s="34">
@@ -28738,7 +28738,7 @@
         <v/>
       </c>
       <c r="K149" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J149,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J149,1))</f>
         <v/>
       </c>
       <c r="L149" s="34">
@@ -28932,7 +28932,7 @@
         <v/>
       </c>
       <c r="K150" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J150,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J150,1))</f>
         <v/>
       </c>
       <c r="L150" s="34">
@@ -29126,7 +29126,7 @@
         <v/>
       </c>
       <c r="K151" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J151,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J151,1))</f>
         <v/>
       </c>
       <c r="L151" s="34">
@@ -29306,7 +29306,7 @@
         <v/>
       </c>
       <c r="K152" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J152,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J152,1))</f>
         <v/>
       </c>
       <c r="L152" s="34">
@@ -29488,7 +29488,7 @@
         <v/>
       </c>
       <c r="K153" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J153,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J153,1))</f>
         <v/>
       </c>
       <c r="L153" s="34">
@@ -29670,7 +29670,7 @@
         <v/>
       </c>
       <c r="K154" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J154,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J154,1))</f>
         <v/>
       </c>
       <c r="L154" s="34">
@@ -29850,7 +29850,7 @@
         <v/>
       </c>
       <c r="K155" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J155,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J155,1))</f>
         <v/>
       </c>
       <c r="L155" s="34">
@@ -30032,7 +30032,7 @@
         <v/>
       </c>
       <c r="K156" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J156,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J156,1))</f>
         <v/>
       </c>
       <c r="L156" s="34">
@@ -30212,7 +30212,7 @@
         <v/>
       </c>
       <c r="K157" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J157,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J157,1))</f>
         <v/>
       </c>
       <c r="L157" s="34">
@@ -30394,7 +30394,7 @@
         <v/>
       </c>
       <c r="K158" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J158,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J158,1))</f>
         <v/>
       </c>
       <c r="L158" s="34">
@@ -30576,7 +30576,7 @@
         <v/>
       </c>
       <c r="K159" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J159,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J159,1))</f>
         <v/>
       </c>
       <c r="L159" s="34">
@@ -30758,7 +30758,7 @@
         <v/>
       </c>
       <c r="K160" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J160,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J160,1))</f>
         <v/>
       </c>
       <c r="L160" s="34">
@@ -30944,7 +30944,7 @@
         <v/>
       </c>
       <c r="K161" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J161,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J161,1))</f>
         <v/>
       </c>
       <c r="L161" s="34">
@@ -31130,7 +31130,7 @@
         <v/>
       </c>
       <c r="K162" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J162,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J162,1))</f>
         <v/>
       </c>
       <c r="L162" s="34">
@@ -31312,7 +31312,7 @@
         <v/>
       </c>
       <c r="K163" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J163,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J163,1))</f>
         <v/>
       </c>
       <c r="L163" s="34">
@@ -31488,7 +31488,7 @@
         <v/>
       </c>
       <c r="K164" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J164,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J164,1))</f>
         <v/>
       </c>
       <c r="L164" s="34">
@@ -31664,7 +31664,7 @@
         <v/>
       </c>
       <c r="K165" s="34">
-        <f>MIN(16,FLOOR(60*service_hr/J165,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J165,1))</f>
         <v/>
       </c>
       <c r="L165" s="34">
@@ -31850,7 +31850,7 @@
         <v/>
       </c>
       <c r="K166" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J166,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J166,1))</f>
         <v/>
       </c>
       <c r="L166" s="34">
@@ -32032,7 +32032,7 @@
         <v/>
       </c>
       <c r="K167" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J167,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J167,1))</f>
         <v/>
       </c>
       <c r="L167" s="34">
@@ -32212,7 +32212,7 @@
         <v/>
       </c>
       <c r="K168" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J168,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J168,1))</f>
         <v/>
       </c>
       <c r="L168" s="34">
@@ -32392,7 +32392,7 @@
         <v/>
       </c>
       <c r="K169" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J169,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J169,1))</f>
         <v/>
       </c>
       <c r="L169" s="34">
@@ -32574,7 +32574,7 @@
         <v/>
       </c>
       <c r="K170" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J170,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J170,1))</f>
         <v/>
       </c>
       <c r="L170" s="34">
@@ -32768,7 +32768,7 @@
         <v/>
       </c>
       <c r="K171" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J171,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J171,1))</f>
         <v/>
       </c>
       <c r="L171" s="34">
@@ -32962,7 +32962,7 @@
         <v/>
       </c>
       <c r="K172" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J172,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J172,1))</f>
         <v/>
       </c>
       <c r="L172" s="34">
@@ -33156,7 +33156,7 @@
         <v/>
       </c>
       <c r="K173" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J173,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J173,1))</f>
         <v/>
       </c>
       <c r="L173" s="34">
@@ -33350,7 +33350,7 @@
         <v/>
       </c>
       <c r="K174" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J174,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J174,1))</f>
         <v/>
       </c>
       <c r="L174" s="34">
@@ -33544,7 +33544,7 @@
         <v/>
       </c>
       <c r="K175" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J175,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J175,1))</f>
         <v/>
       </c>
       <c r="L175" s="34">
@@ -33738,7 +33738,7 @@
         <v/>
       </c>
       <c r="K176" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J176,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J176,1))</f>
         <v/>
       </c>
       <c r="L176" s="34">
@@ -33932,7 +33932,7 @@
         <v/>
       </c>
       <c r="K177" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J177,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J177,1))</f>
         <v/>
       </c>
       <c r="L177" s="34">
@@ -34126,7 +34126,7 @@
         <v/>
       </c>
       <c r="K178" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J178,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J178,1))</f>
         <v/>
       </c>
       <c r="L178" s="34">
@@ -34320,7 +34320,7 @@
         <v/>
       </c>
       <c r="K179" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J179,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J179,1))</f>
         <v/>
       </c>
       <c r="L179" s="34">
@@ -34514,7 +34514,7 @@
         <v/>
       </c>
       <c r="K180" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J180,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J180,1))</f>
         <v/>
       </c>
       <c r="L180" s="34">
@@ -34708,7 +34708,7 @@
         <v/>
       </c>
       <c r="K181" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J181,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J181,1))</f>
         <v/>
       </c>
       <c r="L181" s="34">
@@ -34902,7 +34902,7 @@
         <v/>
       </c>
       <c r="K182" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J182,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J182,1))</f>
         <v/>
       </c>
       <c r="L182" s="34">
@@ -35096,7 +35096,7 @@
         <v/>
       </c>
       <c r="K183" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J183,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J183,1))</f>
         <v/>
       </c>
       <c r="L183" s="34">
@@ -35290,7 +35290,7 @@
         <v/>
       </c>
       <c r="K184" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J184,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J184,1))</f>
         <v/>
       </c>
       <c r="L184" s="34">
@@ -35484,7 +35484,7 @@
         <v/>
       </c>
       <c r="K185" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J185,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J185,1))</f>
         <v/>
       </c>
       <c r="L185" s="34">
@@ -35678,7 +35678,7 @@
         <v/>
       </c>
       <c r="K186" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J186,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J186,1))</f>
         <v/>
       </c>
       <c r="L186" s="34">
@@ -35872,7 +35872,7 @@
         <v/>
       </c>
       <c r="K187" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J187,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J187,1))</f>
         <v/>
       </c>
       <c r="L187" s="34">
@@ -36066,7 +36066,7 @@
         <v/>
       </c>
       <c r="K188" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J188,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J188,1))</f>
         <v/>
       </c>
       <c r="L188" s="34">
@@ -36260,7 +36260,7 @@
         <v/>
       </c>
       <c r="K189" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J189,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J189,1))</f>
         <v/>
       </c>
       <c r="L189" s="34">
@@ -36454,7 +36454,7 @@
         <v/>
       </c>
       <c r="K190" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J190,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J190,1))</f>
         <v/>
       </c>
       <c r="L190" s="34">
@@ -36648,7 +36648,7 @@
         <v/>
       </c>
       <c r="K191" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J191,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J191,1))</f>
         <v/>
       </c>
       <c r="L191" s="34">
@@ -36842,7 +36842,7 @@
         <v/>
       </c>
       <c r="K192" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J192,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J192,1))</f>
         <v/>
       </c>
       <c r="L192" s="34">
@@ -37036,7 +37036,7 @@
         <v/>
       </c>
       <c r="K193" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J193,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J193,1))</f>
         <v/>
       </c>
       <c r="L193" s="34">
@@ -37230,7 +37230,7 @@
         <v/>
       </c>
       <c r="K194" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J194,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J194,1))</f>
         <v/>
       </c>
       <c r="L194" s="34">
@@ -37424,7 +37424,7 @@
         <v/>
       </c>
       <c r="K195" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J195,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J195,1))</f>
         <v/>
       </c>
       <c r="L195" s="34">
@@ -37608,7 +37608,7 @@
         <v/>
       </c>
       <c r="K196" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J196,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J196,1))</f>
         <v/>
       </c>
       <c r="L196" s="34">
@@ -37774,7 +37774,7 @@
         <v/>
       </c>
       <c r="K197" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J197,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J197,1))</f>
         <v/>
       </c>
       <c r="L197" s="34">
@@ -37950,7 +37950,7 @@
         <v/>
       </c>
       <c r="K198" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J198,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J198,1))</f>
         <v/>
       </c>
       <c r="L198" s="34">
@@ -38144,7 +38144,7 @@
         <v/>
       </c>
       <c r="K199" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J199,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J199,1))</f>
         <v/>
       </c>
       <c r="L199" s="34">
@@ -38338,7 +38338,7 @@
         <v/>
       </c>
       <c r="K200" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J200,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J200,1))</f>
         <v/>
       </c>
       <c r="L200" s="34">
@@ -38532,7 +38532,7 @@
         <v/>
       </c>
       <c r="K201" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J201,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J201,1))</f>
         <v/>
       </c>
       <c r="L201" s="34">
@@ -38716,7 +38716,7 @@
         <v/>
       </c>
       <c r="K202" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J202,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J202,1))</f>
         <v/>
       </c>
       <c r="L202" s="34">
@@ -38882,7 +38882,7 @@
         <v/>
       </c>
       <c r="K203" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J203,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J203,1))</f>
         <v/>
       </c>
       <c r="L203" s="34">
@@ -39058,7 +39058,7 @@
         <v/>
       </c>
       <c r="K204" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J204,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J204,1))</f>
         <v/>
       </c>
       <c r="L204" s="34">
@@ -39252,7 +39252,7 @@
         <v/>
       </c>
       <c r="K205" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J205,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J205,1))</f>
         <v/>
       </c>
       <c r="L205" s="34">
@@ -40267,7 +40267,7 @@
         </is>
       </c>
       <c r="C11" s="39" t="n">
-        <v>0.1041</v>
+        <v>0.104</v>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>

--- a/finance/_refresh_bolt.xlsx
+++ b/finance/_refresh_bolt.xlsx
@@ -1332,7 +1332,7 @@
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>Cap on revenue sailings/day — MID headline duty cycle; thin=12 / full=18 bookends in _utilization_scenarios (Jaideep 2026-06-21).</t>
+          <t>Cap on revenue sailings/day — 15 across thin/mid/full scenarios (Jaideep 2026-06-21).</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
         <v>0.7</v>
       </c>
       <c r="C33" s="19" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>

--- a/finance/_refresh_bolt.xlsx
+++ b/finance/_refresh_bolt.xlsx
@@ -27,23 +27,23 @@
     <definedName name="dwell_min">'Assumptions'!$B$18</definedName>
     <definedName name="max_tpd">'Assumptions'!$B$19</definedName>
     <definedName name="crew_factor">'Assumptions'!$B$20</definedName>
-    <definedName name="ins_pct">'Assumptions'!$B$21</definedName>
-    <definedName name="charge_berth">'Assumptions'!$B$22</definedName>
-    <definedName name="mech_uptime">'Assumptions'!$B$23</definedName>
-    <definedName name="capture">'Assumptions'!$B$24</definedName>
-    <definedName name="capture_captive">'Assumptions'!$B$25</definedName>
-    <definedName name="discount">'Assumptions'!$B$26</definedName>
-    <definedName name="diesel_co2pg">'Assumptions'!$B$27</definedName>
-    <definedName name="load_thin">'Assumptions'!$B$31</definedName>
-    <definedName name="revleg_thin">'Assumptions'!$C$31</definedName>
-    <definedName name="load_mid">'Assumptions'!$B$32</definedName>
-    <definedName name="revleg_mid">'Assumptions'!$C$32</definedName>
-    <definedName name="load_full">'Assumptions'!$B$33</definedName>
-    <definedName name="revleg_full">'Assumptions'!$C$33</definedName>
-    <definedName name="band_tbl">'Assumptions'!$A$31:$C$33</definedName>
-    <definedName name="scenario">'Assumptions'!$B$35</definedName>
-    <definedName name="load_sel">'Assumptions'!$B$36</definedName>
-    <definedName name="revleg_sel">'Assumptions'!$B$37</definedName>
+    <definedName name="mech_uptime">'Assumptions'!$B$21</definedName>
+    <definedName name="capture">'Assumptions'!$B$22</definedName>
+    <definedName name="capture_captive">'Assumptions'!$B$23</definedName>
+    <definedName name="discount">'Assumptions'!$B$24</definedName>
+    <definedName name="diesel_co2pg">'Assumptions'!$B$25</definedName>
+    <definedName name="ins_pct">'Assumptions'!$B$29</definedName>
+    <definedName name="charge_berth">'Assumptions'!$B$30</definedName>
+    <definedName name="load_thin">'Assumptions'!$B$34</definedName>
+    <definedName name="revleg_thin">'Assumptions'!$C$34</definedName>
+    <definedName name="load_mid">'Assumptions'!$B$35</definedName>
+    <definedName name="revleg_mid">'Assumptions'!$C$35</definedName>
+    <definedName name="load_full">'Assumptions'!$B$36</definedName>
+    <definedName name="revleg_full">'Assumptions'!$C$36</definedName>
+    <definedName name="band_tbl">'Assumptions'!$A$34:$C$36</definedName>
+    <definedName name="scenario">'Assumptions'!$B$38</definedName>
+    <definedName name="load_sel">'Assumptions'!$B$39</definedName>
+    <definedName name="revleg_sel">'Assumptions'!$B$40</definedName>
     <definedName name="country_opex">'Country opex'!$A$4:$G$21</definedName>
     <definedName name="som_floor_fleet">'Corridor economics'!$D$228</definedName>
     <definedName name="som_floor_rev">'Corridor economics'!$E$228</definedName>
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B27"/>
+  <dimension ref="B2:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -786,84 +786,143 @@
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>EBITDA  = REVENUE − OPEX   (energy + captain + marina/overhead + maintenance)</t>
+          <t>EBITDA  = REVENUE − OPEX</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>PAYBACK = vessel CAPEX ÷ EBITDA</t>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    OPEX = energy + crew + berth/port admin + maintenance + vessel insurance + fast-charge berth</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="2" t="inlineStr"/>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>PAYBACK = vessel CAPEX ÷ EBITDA</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>From demand pool to fleet &amp; market size</t>
-        </is>
-      </c>
+      <c r="B17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Navier serviceable rides/yr = corridor demand pool × capture rate (10% on contested corridors; ~90% on captive sole-operator transfer legs — see the per-row Capture % column)</t>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>OPEX lines (per boat, per year — no double-counting)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Vessels supported = FLOOR(Navier rides/yr ÷ pax/yr per boat);  Market rev = vessels × rev/boat. The 'Market sizing' tab rolls these up into the SOM → SAM → TAM ladder.</t>
+          <t>Energy — variable propulsion cost: kWh on revenue sailings × local $/kWh (Country opex tab). Excludes utility demand charges.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Crew — fully-loaded captain + relief: local captain wage × crew FTE factor (Country opex + Assumptions).</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>The scenario toggle (what we flex)</t>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Berth &amp; port admin — fixed annual berth, port fees, and local marine admin (Country opex tab). Excludes vessel H&amp;M+P&amp;I and fast-charge infrastructure.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>'Corridor economics' has a SCENARIO cell = THIN / MID / FULL. It flexes two levers: load factor (how full the boat is) and revenue-leg factor (how many legs earn full fare). MID is the headline. Change that one cell and the whole model recomputes. The right-hand Payback THIN/MID/FULL columns always show all three at once.</t>
+          <t>Maintenance — vessel annual maintenance reserve (Assumptions tab).</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Vessel insurance — commercial H&amp;M + P&amp;I as % of regional CAPEX (Assumptions % × Country opex CAPEX column).</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Colour &amp; provenance legend</t>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Fast-charge berth — dedicated fast-charge berth slot + utility demand charges (Assumptions default; overridable per market). Separate from per-kWh energy and berth/port admin.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Yellow = INPUTS you can change (fare, distance, demand, weather).</t>
-        </is>
-      </c>
+      <c r="B25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Green  = COMPUTED by formula.</t>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>From demand pool to fleet &amp; market size</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Navier serviceable rides/yr = corridor demand pool × capture rate (10% on contested corridors; ~90% on captive sole-operator transfer legs — see the per-row Capture % column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Vessels supported = FLOOR(Navier rides/yr ÷ pax/yr per boat);  Market rev = vessels × rev/boat. The 'Market sizing' tab rolls these up into the SOM → SAM → TAM ladder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>The scenario toggle (what we flex)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>'Corridor economics' has a SCENARIO cell = THIN / MID / FULL. It flexes load factor (occupancy) and revenue-leg factor (share of legs that earn full fare). Max trips/day is fixed across all three bands (see Assumptions). MID is the headline. Change SCENARIO and the whole model recomputes. Payback THIN/MID/FULL columns always show all three at once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Colour &amp; provenance legend</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Yellow = INPUTS you can change (fare, distance, demand, weather).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Green  = COMPUTED by formula.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   Every fare &amp; demand figure carries a Source tier (T1 official → T5 modeled) + Confidence (high/med/low). Null beats a wrong number: no published pool → blank, not a guess.</t>
         </is>
@@ -880,7 +939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1369,11 +1428,11 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Insurance (% of capex/yr)</t>
+          <t>Mechanical uptime</t>
         </is>
       </c>
       <c r="B21" s="17" t="n">
-        <v>0.025</v>
+        <v>0.75</v>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
@@ -1382,7 +1441,7 @@
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
@@ -1392,29 +1451,25 @@
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>H&amp;M + P&amp;I for a commercial passenger vessel ~2.5%/yr of capex; scales with regional capex overrides (Jaideep 2026-06-19).</t>
+          <t>Blade luxury aviation ~75-80% reliability uptime</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Charging &amp; berth (additional to marina+energy)</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="n">
-        <v>18000</v>
+          <t>Navier capture rate</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>0.1</v>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>USD/yr</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
+          <t>frac</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr"/>
       <c r="E22" s="13" t="inlineStr">
         <is>
           <t>med</t>
@@ -1422,29 +1477,25 @@
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>Dedicated fast-charge berth + demand charges, ADDITIONAL to marina overhead and energy (Jaideep 2026-06-19). L3-overridable.</t>
+          <t>Navier wins ~10% of a CONTESTED corridor demand pool (locked). Captive sole-operator transfer legs (captive:true / luxury_charter / hospitality archetypes) carry the captive rate instead — see per-row Capture %.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Mechanical uptime</t>
+          <t>Captive capture rate (A′ corridors)</t>
         </is>
       </c>
       <c r="B23" s="17" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
           <t>frac</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
+      <c r="D23" s="13" t="inlineStr"/>
       <c r="E23" s="13" t="inlineStr">
         <is>
           <t>med</t>
@@ -1452,255 +1503,303 @@
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>Blade luxury aviation ~75-80% reliability uptime</t>
+          <t>Sole-operator water-access-only transfer legs (captive:true or luxury_charter/hospitality archetype): Navier IS the transfer fleet — capture ~90%. Applied per-row in the Capture % column.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Navier capture rate</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="n">
-        <v>0.1</v>
+          <t>Discount factor (vs comparable fare)</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="n">
+        <v>1</v>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
           <t>frac</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr"/>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>Navier wins ~10% of a CONTESTED corridor demand pool (locked). Captive sole-operator transfer legs (captive:true / luxury_charter / hospitality archetypes) carry the captive rate instead — see per-row Capture %.</t>
+          <t>Market parity — better product, not cheaper (locked).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Captive capture rate (A′ corridors)</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="n">
-        <v>0.9</v>
+          <t>Diesel CO₂ per gallon</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="n">
+        <v>10.21</v>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>frac</t>
-        </is>
-      </c>
-      <c r="D25" s="13" t="inlineStr"/>
+          <t>kg/gal</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>Sole-operator water-access-only transfer legs (captive:true or luxury_charter/hospitality archetype): Navier IS the transfer fleet — capture ~90%. Applied per-row in the Capture % column.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>Discount factor (vs comparable fare)</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>frac</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="inlineStr">
-        <is>
-          <t>Market parity — better product, not cheaper (locked).</t>
+          <t>US EPA: 10.21 kg CO2 per gallon marine/diesel</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>Diesel CO₂ per gallon</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n">
-        <v>10.21</v>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>kg/gal</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>US EPA: 10.21 kg CO2 per gallon marine/diesel</t>
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>OPEX defaults  (global fallbacks — localized energy, crew, berth admin on Country opex tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>Conf.</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>Source / note</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>Utilization scenarios  (the two levers we flex)</t>
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>Vessel insurance — H&amp;M + P&amp;I (% of CAPEX/yr)</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>frac</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>Commercial vessel H&amp;M + P&amp;I ~2.5%/yr of regional CAPEX. Separate from berth/port admin in Country opex (Jaideep 2026-06-19).. Multiplied by regional CAPEX (Country opex col G). Not included in berth/port admin.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>Load factor</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>Rev-leg factor</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr"/>
-      <c r="E30" s="10" t="inlineStr"/>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>THIN</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="C31" s="19" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F31" s="14" t="inlineStr">
-        <is>
-          <t>thin/one-way/seasonal corridor — conservative floor</t>
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Fast-charge berth &amp; demand charges (global default)</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>USD/yr</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>Dedicated fast-charge berth slot + utility demand charges. Excludes per-kWh propulsion energy and berth/port admin (Jaideep 2026-06-19). L3-overridable per market.. Dedicated charge berth + utility demand charges. Excludes per-kWh propulsion energy and berth/port admin. L3-overridable per market.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="B32" s="19" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="C32" s="19" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="F32" s="14" t="inlineStr">
-        <is>
-          <t>HEADLINE — realistic busy two-way corridor</t>
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>Utilization scenarios  (load factor + revenue-leg factor)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="inlineStr">
-        <is>
-          <t>FULL</t>
-        </is>
-      </c>
-      <c r="B33" s="19" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C33" s="19" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F33" s="14" t="inlineStr">
-        <is>
-          <t>mature/dense corridor — optimistic ceiling</t>
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Load factor</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Rev-leg factor</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr"/>
+      <c r="E33" s="10" t="inlineStr"/>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>THIN</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C34" s="19" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>thin/one-way/seasonal corridor — conservative floor</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="20" t="inlineStr">
-        <is>
-          <t>SCENARIO (toggle me)</t>
-        </is>
-      </c>
-      <c r="B35" s="21" t="inlineStr">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="C35" s="22" t="inlineStr">
-        <is>
-          <t>← set THIN / MID / FULL</t>
+      <c r="B35" s="19" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C35" s="19" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>HEADLINE — realistic busy two-way corridor</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C36" s="19" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>mature/dense corridor — optimistic ceiling</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>SCENARIO (toggle me)</t>
+        </is>
+      </c>
+      <c r="B38" s="21" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C38" s="22" t="inlineStr">
+        <is>
+          <t>← set THIN / MID / FULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Selected load factor</t>
         </is>
       </c>
-      <c r="B36" s="23">
-        <f>VLOOKUP(scenario,'Assumptions'!$A$31:$C$33,2,FALSE)</f>
+      <c r="B39" s="23">
+        <f>VLOOKUP(scenario,'Assumptions'!$A$34:$C$36,2,FALSE)</f>
         <v/>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>Selected rev-leg factor</t>
         </is>
       </c>
-      <c r="B37" s="23">
-        <f>VLOOKUP(scenario,'Assumptions'!$A$31:$C$33,3,FALSE)</f>
+      <c r="B40" s="23">
+        <f>VLOOKUP(scenario,'Assumptions'!$A$34:$C$36,3,FALSE)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A3:F3"/>
+  <mergeCells count="5">
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A3:F3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="B38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"THIN,MID,FULL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1730,7 +1829,7 @@
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>Country opex — L3 localized layer (VLOOKUP target for the engine)</t>
+          <t>Country opex — localized inputs (crew, energy, berth admin, CAPEX)</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1856,7 @@
       </c>
       <c r="E3" s="24" t="inlineStr">
         <is>
-          <t>Marina $/yr</t>
+          <t>Berth &amp; port admin $/yr</t>
         </is>
       </c>
       <c r="F3" s="24" t="inlineStr">
@@ -1772,7 +1871,7 @@
       </c>
       <c r="H3" s="24" t="inlineStr">
         <is>
-          <t>Source notes (captain | energy | marina)</t>
+          <t>Source notes (crew | energy | berth admin)</t>
         </is>
       </c>
     </row>
@@ -2355,10 +2454,10 @@
     <col width="11" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
     <col width="9" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
     <col width="11" customWidth="1" min="27" max="27"/>
     <col width="10" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
@@ -2519,7 +2618,7 @@
       </c>
       <c r="W3" s="24" t="inlineStr">
         <is>
-          <t>Marina/yr</t>
+          <t>Berth &amp; port admin/yr</t>
         </is>
       </c>
       <c r="X3" s="24" t="inlineStr">
@@ -2529,12 +2628,12 @@
       </c>
       <c r="Y3" s="24" t="inlineStr">
         <is>
-          <t>Insurance/yr</t>
+          <t>Vessel insurance/yr</t>
         </is>
       </c>
       <c r="Z3" s="24" t="inlineStr">
         <is>
-          <t>Charge+berth/yr</t>
+          <t>Fast-charge berth/yr</t>
         </is>
       </c>
       <c r="AA3" s="24" t="inlineStr">
